--- a/artfynd/A 19015-2026 artfynd.xlsx
+++ b/artfynd/A 19015-2026 artfynd.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Stefan Bergström, Suvi Bergström</t>
+          <t>Suvi Bergström, Stefan Bergström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
